--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8576</v>
+        <v>8578</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5985</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="4">

--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8578</v>
+        <v>8579</v>
       </c>
     </row>
     <row r="3">

--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8579</v>
+        <v>8576</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5988</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="4">

--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8576</v>
+        <v>8579</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5985</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="4">

--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8579</v>
+        <v>8589</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5989</v>
+        <v>5997</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">

--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8589</v>
+        <v>8596</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5997</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5">

--- a/aircraft/reports/top-manufacturers-over-time.xlsx
+++ b/aircraft/reports/top-manufacturers-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8596</v>
+        <v>8605</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6001</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
